--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/03_Personal_Rechtekette/06_Rechte_und_Nebentaetigkeiten_Matrix.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/03_Personal_Rechtekette/06_Rechte_und_Nebentaetigkeiten_Matrix.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vertragsvergleich" sheetId="1" r:id="Reed81ecfddaa4c93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anlagenstatus" sheetId="2" r:id="R1772db127bb64393"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aktuelle_Vergütung" sheetId="3" r:id="R5dd3b6ee4cd2450c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vertragsvergleich" sheetId="1" r:id="R155647fd6cd34a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anlagenstatus" sheetId="2" r:id="Rc662fadd13eb4fc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aktuelle_Vergütung" sheetId="3" r:id="R7a8b28bb358d47c8"/>
   </x:sheets>
 </x:workbook>
 </file>
